--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4210" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4251" uniqueCount="771">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:38:17+00:00</t>
+    <t>2026-09-30T10:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -668,6 +668,22 @@
   </si>
   <si>
     <t>statut : [1..1] Code</t>
+  </si>
+  <si>
+    <t>DocumentReference.extension:isDeleted</t>
+  </si>
+  <si>
+    <t>isDeleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted}
+</t>
+  </si>
+  <si>
+    <t>Extension définie pour distinguer les fiches supprimées. Suppression logique pas physique.</t>
+  </si>
+  <si>
+    <t>Extension définie par le volet ANS "Volet Partage de documents de santé en mobilité" sur les ressources List et DocumentReference pour distinguer les lots de soumission et les fiches supprimées. A noter que la suppression est logique et pas physique.</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>
@@ -2721,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS102"/>
+  <dimension ref="A1:AS103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.97265625" customWidth="true" bestFit="true"/>
@@ -5092,14 +5108,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
       </c>
@@ -5108,25 +5126,25 @@
         <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -5177,7 +5195,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -5186,13 +5204,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
@@ -5219,12 +5237,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5232,35 +5250,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -5308,54 +5322,54 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5363,10 +5377,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>98</v>
@@ -5378,16 +5392,20 @@
         <v>98</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -5423,23 +5441,25 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -5448,43 +5468,41 @@
         <v>109</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AR21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AS21" t="s" s="2">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5505,13 +5523,13 @@
         <v>98</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5550,19 +5568,17 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -5577,72 +5593,72 @@
         <v>109</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>98</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5667,11 +5683,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -5689,13 +5707,13 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
@@ -5704,39 +5722,39 @@
         <v>109</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AS23" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5744,16 +5762,16 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>98</v>
@@ -5762,13 +5780,13 @@
         <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5794,13 +5812,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5818,10 +5834,10 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>97</v>
@@ -5833,39 +5849,39 @@
         <v>109</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AS24" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5873,13 +5889,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -5888,16 +5904,16 @@
         <v>98</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5923,11 +5939,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5945,7 +5963,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5957,46 +5975,46 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -6015,16 +6033,16 @@
         <v>98</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6054,7 +6072,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -6072,58 +6090,58 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AP26" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -6142,15 +6160,17 @@
         <v>98</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -6175,13 +6195,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -6199,58 +6217,58 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AR27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS27" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -6269,17 +6287,15 @@
         <v>98</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -6328,7 +6344,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6343,50 +6359,50 @@
         <v>109</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AS28" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>97</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>98</v>
@@ -6398,16 +6414,16 @@
         <v>98</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>309</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6457,13 +6473,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -6472,39 +6488,39 @@
         <v>109</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6512,10 +6528,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>98</v>
@@ -6524,19 +6540,19 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6586,13 +6602,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -6601,39 +6617,39 @@
         <v>109</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR30" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6641,13 +6657,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -6656,16 +6672,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6715,7 +6731,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6730,39 +6746,39 @@
         <v>109</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AR31" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6770,31 +6786,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6844,54 +6860,54 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6902,27 +6918,29 @@
         <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>346</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>112</v>
+        <v>347</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6971,34 +6989,34 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>114</v>
+        <v>345</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>115</v>
+        <v>353</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -7010,26 +7028,26 @@
         <v>82</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -7041,17 +7059,15 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -7100,19 +7116,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -7144,14 +7160,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>352</v>
+        <v>117</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -7164,26 +7180,24 @@
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>118</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>353</v>
+        <v>119</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O35" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -7231,7 +7245,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -7258,7 +7272,7 @@
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -7275,33 +7289,33 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>358</v>
@@ -7310,9 +7324,11 @@
         <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -7336,58 +7352,58 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AG36" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>366</v>
+        <v>198</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -7399,15 +7415,15 @@
         <v>82</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7430,15 +7446,17 @@
         <v>98</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>369</v>
+        <v>175</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -7463,13 +7481,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -7487,54 +7505,54 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
+      <c r="AL37" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS37" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AK37" t="s" s="2">
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7542,13 +7560,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -7557,20 +7575,16 @@
         <v>98</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>374</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -7618,34 +7632,34 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="AL38" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -7654,18 +7668,18 @@
         <v>82</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7673,10 +7687,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>98</v>
@@ -7688,19 +7702,19 @@
         <v>98</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7725,11 +7739,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7747,13 +7763,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -7762,39 +7778,39 @@
         <v>109</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7805,7 +7821,7 @@
         <v>97</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>98</v>
@@ -7817,16 +7833,20 @@
         <v>98</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>264</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7850,13 +7870,11 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7874,10 +7892,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>84</v>
@@ -7889,34 +7907,34 @@
         <v>109</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AP40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AS40" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>404</v>
       </c>
@@ -7929,28 +7947,28 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>346</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>112</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>113</v>
+        <v>406</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -8001,19 +8019,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>114</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -8025,10 +8043,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>115</v>
+        <v>408</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -8045,21 +8063,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -8071,17 +8089,15 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -8130,19 +8146,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -8174,14 +8190,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>352</v>
+        <v>117</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -8194,26 +8210,24 @@
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>118</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>119</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -8261,7 +8275,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8288,7 +8302,7 @@
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -8305,42 +8319,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>408</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -8388,19 +8406,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -8412,30 +8430,30 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>403</v>
+        <v>198</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8443,7 +8461,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>97</v>
@@ -8455,16 +8473,16 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>413</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>414</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
+        <v>415</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8515,10 +8533,10 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>114</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>97</v>
@@ -8527,7 +8545,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -8539,41 +8557,41 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>115</v>
+        <v>408</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -8585,17 +8603,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8632,31 +8648,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8688,21 +8704,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8711,21 +8727,21 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>119</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8737,7 +8753,7 @@
         <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>82</v>
@@ -8749,78 +8765,78 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8834,7 +8850,7 @@
         <v>97</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8846,14 +8862,14 @@
         <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8866,7 +8882,7 @@
         <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>82</v>
@@ -8878,13 +8894,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>180</v>
+        <v>427</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>181</v>
+        <v>428</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8902,7 +8918,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8917,10 +8933,10 @@
         <v>109</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
@@ -8929,7 +8945,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8938,18 +8954,18 @@
         <v>82</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8957,34 +8973,32 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>438</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8997,7 +9011,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9009,13 +9023,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9033,7 +9047,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9048,10 +9062,10 @@
         <v>109</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -9060,7 +9074,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -9069,7 +9083,7 @@
         <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9077,10 +9091,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9088,10 +9102,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -9100,22 +9114,22 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9128,7 +9142,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9164,7 +9178,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9176,13 +9190,13 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>454</v>
+        <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -9191,7 +9205,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9200,7 +9214,7 @@
         <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -9208,10 +9222,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9234,19 +9248,19 @@
         <v>98</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9259,7 +9273,7 @@
         <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>82</v>
@@ -9295,7 +9309,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9307,13 +9321,13 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>109</v>
+        <v>459</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
@@ -9322,7 +9336,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9331,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9339,10 +9353,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9365,19 +9379,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9426,7 +9440,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9444,7 +9458,7 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -9453,7 +9467,7 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -9470,10 +9484,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9496,17 +9510,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>111</v>
+        <v>443</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9519,7 +9535,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -9555,7 +9571,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9570,10 +9586,10 @@
         <v>109</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -9582,7 +9598,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9597,12 +9613,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9616,7 +9632,7 @@
         <v>97</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -9625,17 +9641,17 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>486</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9648,7 +9664,7 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -9684,7 +9700,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9699,10 +9715,10 @@
         <v>109</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -9711,7 +9727,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9728,10 +9744,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9754,18 +9770,18 @@
         <v>98</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>153</v>
+        <v>491</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9789,59 +9805,61 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>82</v>
@@ -9850,15 +9868,15 @@
         <v>82</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9881,16 +9899,16 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>341</v>
+        <v>153</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9916,13 +9934,11 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9940,38 +9956,38 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>109</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AQ56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9979,10 +9995,10 @@
         <v>82</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>508</v>
       </c>
@@ -9995,30 +10011,32 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>111</v>
+        <v>346</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>112</v>
+        <v>509</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -10067,7 +10085,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>114</v>
+        <v>508</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -10079,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -10094,7 +10112,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>115</v>
+        <v>512</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -10111,21 +10129,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -10137,17 +10155,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -10196,19 +10212,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -10240,14 +10256,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>352</v>
+        <v>117</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -10260,26 +10276,24 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>118</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>119</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -10327,7 +10341,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10354,7 +10368,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -10371,14 +10385,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10391,22 +10405,26 @@
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>512</v>
+        <v>118</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>513</v>
+        <v>358</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -10454,7 +10472,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>511</v>
+        <v>361</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10466,28 +10484,28 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>518</v>
+        <v>198</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>82</v>
@@ -10498,10 +10516,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10524,17 +10542,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>259</v>
+        <v>517</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -10559,13 +10575,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -10583,7 +10599,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10595,42 +10611,42 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>526</v>
+        <v>109</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10638,30 +10654,32 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>532</v>
+        <v>264</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -10686,13 +10704,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -10710,54 +10728,54 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AG62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>109</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AP62" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS62" t="s" s="2">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>539</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10765,28 +10783,28 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>111</v>
+        <v>537</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>112</v>
+        <v>538</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>113</v>
+        <v>539</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10837,7 +10855,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>114</v>
+        <v>536</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10849,7 +10867,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10861,13 +10879,13 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>115</v>
+        <v>541</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>82</v>
@@ -10876,26 +10894,26 @@
         <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10907,17 +10925,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10954,31 +10970,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -11010,21 +11026,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -11033,19 +11049,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>486</v>
+        <v>118</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>542</v>
+        <v>119</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>543</v>
+        <v>120</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>544</v>
+        <v>121</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -11083,37 +11099,37 @@
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>125</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -11122,7 +11138,7 @@
         <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>549</v>
+        <v>115</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -11131,7 +11147,7 @@
         <v>82</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AS65" t="s" s="2">
         <v>82</v>
@@ -11139,10 +11155,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11150,7 +11166,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>97</v>
@@ -11165,24 +11181,22 @@
         <v>98</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q66" t="s" s="2">
-        <v>555</v>
-      </c>
+      <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
         <v>82</v>
       </c>
@@ -11226,7 +11240,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11235,16 +11249,16 @@
         <v>97</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -11253,7 +11267,7 @@
         <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
@@ -11262,18 +11276,18 @@
         <v>82</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="AS66" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11281,35 +11295,39 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>491</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>82</v>
       </c>
@@ -11329,11 +11347,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -11360,45 +11380,45 @@
         <v>97</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AJ67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AK67" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AS67" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11421,20 +11441,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -11462,7 +11478,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -11480,37 +11496,37 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AG68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="AL68" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>82</v>
@@ -11519,15 +11535,15 @@
         <v>82</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11550,16 +11566,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L69" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11583,13 +11603,11 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11607,7 +11625,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11619,25 +11637,25 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>109</v>
+        <v>570</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>294</v>
+        <v>573</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>295</v>
+        <v>574</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>296</v>
+        <v>573</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
@@ -11649,7 +11667,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>584</v>
       </c>
@@ -11662,13 +11680,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -11677,13 +11695,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>111</v>
+        <v>585</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>112</v>
+        <v>586</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>113</v>
+        <v>587</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11734,7 +11752,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>114</v>
+        <v>584</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11746,7 +11764,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -11758,13 +11776,13 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11773,26 +11791,26 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -11804,17 +11822,15 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11851,31 +11867,31 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11907,21 +11923,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11930,19 +11946,19 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>587</v>
+        <v>119</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11980,37 +11996,37 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>590</v>
+        <v>125</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
@@ -12019,7 +12035,7 @@
         <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
@@ -12036,10 +12052,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12062,16 +12078,16 @@
         <v>98</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12097,13 +12113,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -12121,7 +12137,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -12130,7 +12146,7 @@
         <v>97</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>109</v>
@@ -12139,7 +12155,7 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
@@ -12165,10 +12181,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12191,16 +12207,16 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12226,13 +12242,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -12268,7 +12284,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12277,7 +12293,7 @@
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>606</v>
+        <v>198</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>82</v>
@@ -12294,10 +12310,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12320,16 +12336,16 @@
         <v>98</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12379,7 +12395,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12397,7 +12413,7 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
@@ -12406,7 +12422,7 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>198</v>
+        <v>611</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>82</v>
@@ -12437,28 +12453,28 @@
         <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12496,25 +12512,25 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -12526,19 +12542,19 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>621</v>
+        <v>198</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>82</v>
@@ -12547,19 +12563,17 @@
         <v>82</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -12571,7 +12585,7 @@
         <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -12580,16 +12594,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12627,19 +12641,19 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12657,19 +12671,19 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>82</v>
@@ -12678,17 +12692,19 @@
         <v>82</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -12697,7 +12713,7 @@
         <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -12709,15 +12725,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>618</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>631</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -12766,37 +12784,37 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>114</v>
+        <v>617</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>115</v>
+        <v>626</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>82</v>
@@ -12805,26 +12823,26 @@
         <v>82</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -12836,17 +12854,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12883,31 +12899,31 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -12939,21 +12955,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12962,19 +12978,19 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>587</v>
+        <v>119</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13012,31 +13028,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>590</v>
+        <v>125</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -13051,7 +13067,7 @@
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>82</v>
@@ -13068,10 +13084,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13094,16 +13110,16 @@
         <v>98</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13129,13 +13145,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -13153,7 +13169,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13162,7 +13178,7 @@
         <v>97</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>109</v>
@@ -13195,12 +13211,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13214,7 +13230,7 @@
         <v>97</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -13223,16 +13239,16 @@
         <v>98</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13258,13 +13274,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -13309,7 +13325,7 @@
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>606</v>
+        <v>198</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -13324,12 +13340,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13343,24 +13359,26 @@
         <v>97</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>112</v>
+        <v>606</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>608</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -13409,7 +13427,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>114</v>
+        <v>609</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13421,7 +13439,7 @@
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -13436,7 +13454,7 @@
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>115</v>
+        <v>611</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>82</v>
@@ -13453,21 +13471,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -13479,17 +13497,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -13526,31 +13542,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -13582,46 +13598,44 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>643</v>
+        <v>119</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>644</v>
+        <v>120</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -13645,43 +13659,43 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>649</v>
+        <v>125</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -13696,7 +13710,7 @@
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>650</v>
+        <v>115</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
@@ -13705,7 +13719,7 @@
         <v>82</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AS85" t="s" s="2">
         <v>82</v>
@@ -13713,10 +13727,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13733,25 +13747,25 @@
         <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -13776,13 +13790,13 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -13800,7 +13814,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13827,7 +13841,7 @@
         <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>82</v>
@@ -13836,7 +13850,7 @@
         <v>82</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>660</v>
+        <v>198</v>
       </c>
       <c r="AS86" t="s" s="2">
         <v>82</v>
@@ -13844,10 +13858,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13867,19 +13881,23 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13903,13 +13921,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>663</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13945,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>114</v>
+        <v>664</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13939,7 +13957,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13954,7 +13972,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>115</v>
+        <v>655</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -13963,7 +13981,7 @@
         <v>82</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="AS87" t="s" s="2">
         <v>82</v>
@@ -13971,21 +13989,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13997,17 +14015,15 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -14044,31 +14060,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -14100,14 +14116,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -14123,23 +14139,21 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>667</v>
+        <v>119</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>668</v>
+        <v>120</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>670</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -14175,19 +14189,19 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>671</v>
+        <v>125</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14199,7 +14213,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -14214,7 +14228,7 @@
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>672</v>
+        <v>115</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>82</v>
@@ -14223,7 +14237,7 @@
         <v>82</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>673</v>
+        <v>82</v>
       </c>
       <c r="AS89" t="s" s="2">
         <v>82</v>
@@ -14231,10 +14245,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14245,7 +14259,7 @@
         <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -14254,19 +14268,23 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>672</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>673</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>675</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -14314,19 +14332,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>114</v>
+        <v>676</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -14341,7 +14359,7 @@
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>115</v>
+        <v>677</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>82</v>
@@ -14350,7 +14368,7 @@
         <v>82</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AS90" t="s" s="2">
         <v>82</v>
@@ -14358,21 +14376,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -14384,17 +14402,15 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14431,31 +14447,31 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -14487,21 +14503,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -14510,23 +14526,21 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>680</v>
+        <v>119</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>681</v>
+        <v>120</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -14535,7 +14549,7 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>82</v>
@@ -14562,31 +14576,31 @@
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -14601,7 +14615,7 @@
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>686</v>
+        <v>115</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -14610,7 +14624,7 @@
         <v>82</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="AS92" t="s" s="2">
         <v>82</v>
@@ -14618,10 +14632,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14644,18 +14658,20 @@
         <v>98</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -14664,7 +14680,7 @@
         <v>82</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>82</v>
+        <v>689</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>82</v>
@@ -14703,7 +14719,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14730,27 +14746,27 @@
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR93" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AS93" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AS93" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14764,7 +14780,7 @@
         <v>97</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>82</v>
@@ -14773,18 +14789,18 @@
         <v>98</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -14832,7 +14848,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14859,7 +14875,7 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>269</v>
+        <v>699</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -14868,18 +14884,18 @@
         <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AS94" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="AS94" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14893,7 +14909,7 @@
         <v>97</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -14902,17 +14918,17 @@
         <v>98</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14961,7 +14977,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -14988,7 +15004,7 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>709</v>
+        <v>274</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
@@ -14997,7 +15013,7 @@
         <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15005,10 +15021,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15031,19 +15047,17 @@
         <v>98</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>713</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>716</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15092,7 +15106,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15119,7 +15133,7 @@
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
@@ -15128,7 +15142,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15136,10 +15150,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15162,19 +15176,19 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>718</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15223,7 +15237,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15250,7 +15264,7 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
@@ -15259,18 +15273,18 @@
         <v>82</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15284,7 +15298,7 @@
         <v>97</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -15293,19 +15307,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15318,7 +15332,7 @@
         <v>82</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>736</v>
+        <v>82</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>82</v>
@@ -15354,7 +15368,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15381,7 +15395,7 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -15390,7 +15404,7 @@
         <v>82</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15398,10 +15412,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15409,7 +15423,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>97</v>
@@ -15424,18 +15438,20 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -15447,7 +15463,7 @@
         <v>82</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>82</v>
@@ -15483,7 +15499,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15510,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -15519,18 +15535,18 @@
         <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15538,13 +15554,13 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -15553,15 +15569,17 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>532</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>748</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>749</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15574,7 +15592,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>82</v>
+        <v>750</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -15610,7 +15628,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15637,7 +15655,7 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
@@ -15646,7 +15664,7 @@
         <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15654,10 +15672,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15680,17 +15698,15 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>333</v>
+        <v>537</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>760</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15739,7 +15755,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15766,7 +15782,7 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -15775,7 +15791,7 @@
         <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15783,10 +15799,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15809,16 +15825,16 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>338</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>608</v>
+        <v>763</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>609</v>
+        <v>764</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>610</v>
+        <v>765</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15868,7 +15884,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>611</v>
+        <v>766</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15895,23 +15911,152 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AS102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS102" t="s" s="2">
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS103" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS102">
+  <autoFilter ref="A1:AS103">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15921,7 +16066,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI101">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:37:32+00:00</t>
+    <t>2026-09-30T12:38:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:48+00:00</t>
+    <t>2026-09-30T12:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -287,7 +287,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-isarchived-status:Lorsque l'extension PDSm_IsArchived vaut true, l'élément status doit valoir current ou superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).exists() implies (status = 'current' or status = 'superseded')}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
   </si>
   <si>
     <t>Fiche</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:48:42+00:00</t>
+    <t>2026-09-30T13:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -287,7 +287,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-isarchived-status:Lorsque l'extension PDSm_IsArchived vaut true, l'élément status doit valoir current ou superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).exists() implies (status = 'current' or status = 'superseded')}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
   </si>
   <si>
     <t>Fiche</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T13:49:36+00:00</t>
+    <t>2026-09-30T15:53:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -287,7 +287,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}constr-cdr-isdeleted-isarchived:Une fiche supprimée logiquement (extension PDSm_IsDeleted à true) ne peut pas être archivée (extension PDSm_IsArchived à true). {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).empty()}</t>
   </si>
   <si>
     <t>Fiche</t>
@@ -683,7 +683,7 @@
     <t>Extension définie pour distinguer les fiches supprimées. Suppression logique pas physique.</t>
   </si>
   <si>
-    <t>Extension définie par le volet ANS "Volet Partage de documents de santé en mobilité" sur les ressources List et DocumentReference pour distinguer les lots de soumission et les fiches supprimées. A noter que la suppression est logique et pas physique.</t>
+    <t>Extension définie par le volet ANS "Volet Partage de documents de santé en mobilité" sur la ressource DocumentReference pour distinguer les fiches supprimées. A noter que la suppression est logique et pas physique.</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T15:53:21+00:00</t>
+    <t>2026-10-01T13:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:59:48+00:00</t>
+    <t>2026-10-01T15:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T15:54:53+00:00</t>
+    <t>2026-10-05T14:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:15:07+00:00</t>
+    <t>2026-10-05T14:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:43:16+00:00</t>
+    <t>2026-10-05T15:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T15:33:11+00:00</t>
+    <t>2026-10-07T16:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/add-ext-deleted/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T16:07:50+00:00</t>
+    <t>2026-10-08T08:40:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
